--- a/stick-world/config/excel/平衡变量.xlsx
+++ b/stick-world/config/excel/平衡变量.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="variables" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="平衡变量" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/stick-world/config/excel/平衡变量.xlsx
+++ b/stick-world/config/excel/平衡变量.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -453,538 +453,132 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>max</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>step</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>类别</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>当前值</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>最小值</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>最大值</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>步长</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>var_attack_base</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>combat</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="D3" s="2" t="n">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>var_game_speed</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>基础攻击力</t>
+      <c r="D3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>游戏速度倍率</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>var_defense_base</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>combat</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D4" s="2" t="n">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>var_day_duration</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F4" s="2" t="n">
+      <c r="E4" t="n">
+        <v>60</v>
+      </c>
+      <c r="F4" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>基础防御力</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>var_tax_rate</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>economy</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>基础税率</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>var_trade_efficiency</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>economy</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>贸易效率倍率</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>var_research_speed</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>tech</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>科技研究速度倍率</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>var_tech_cost_scale</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>tech</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>科技研究基础消耗</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>var_org_maintenance</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>org</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>组织每回合维护费</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>var_org_loyalty_decay</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>org</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>组织忠诚度每回合衰减</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>var_expand_cost_base</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>expansion</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>扩张基础消耗</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>var_expand_cooldown</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>expansion</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>扩张冷却回合数</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>var_supply_range</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>logistics</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>补给线最大范围</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>var_transport_speed</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>logistics</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>运输速度倍率</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>var_pop_growth_rate</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>人口增长率</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>var_pop_happiness_base</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>基础幸福度</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>var_game_speed</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>游戏速度倍率</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>var_day_duration</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>每回合代表天数</t>
         </is>

--- a/stick-world/config/excel/平衡变量.xlsx
+++ b/stick-world/config/excel/平衡变量.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="平衡变量" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variables" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -455,132 +455,980 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>max</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>description</t>
+          <t>#output_dir: balance</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>类别</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>当前值</t>
+          <t>value</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>最小值</t>
+          <t>min</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>最大值</t>
+          <t>max</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>步长</t>
+          <t>step</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t>description</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>var_game_speed</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>global</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.25</v>
+          <t>类别</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>当前值</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>最小值</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>最大值</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>步长</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>游戏速度倍率</t>
+          <t>描述</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>var_game_speed</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>游戏速度倍率</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>var_day_duration</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>global</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C5" t="n">
         <v>10</v>
       </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
         <v>60</v>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>每回合代表天数</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>var_attack_base</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>combat</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>100</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>基础攻击力</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>var_defense_base</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>combat</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>基础防御力</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>var_tax_rate</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>基础税率</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>var_trade_efficiency</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>贸易效率倍率</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>var_org_maintenance</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>org</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>100</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>组织每回合维护费</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>var_org_loyalty_decay</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>org</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>组织忠诚度每回合衰减</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>var_expand_cost_base</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>expansion</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>200</v>
+      </c>
+      <c r="D12" t="n">
+        <v>50</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>扩张基础消耗</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>var_expand_cooldown</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>expansion</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>30</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>扩张冷却回合数</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>var_supply_range</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>补给线最大范围</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>var_transport_speed</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>运输速度倍率</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>var_pop_happiness_base</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>50</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>100</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>基础幸福度</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>var_arrow_vx</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>combat</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>850</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>抛物线箭矢水平分速（px/s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>var_arrow_gravity</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>combat</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>抛物线箭矢重力（px/s²）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>var_arrow_lead_factor</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>combat</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>箭矢预判系数</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>var_block_chance</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>combat</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>盾牌格挡率（被命中减伤概率）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>var_block_damage_factor</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>combat</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>格挡减伤系数（剩余伤害比例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>var_block_reset_interval</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>combat</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>格挡重置间隔（s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>var_block_front_dot</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>combat</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>正面格挡判定方向余弦阈值</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>var_hitstop_time_scale</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>combat</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>命中顿帧时间缩放</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>var_hitstop_duration</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>combat</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>命中顿帧时长（s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>var_hitstop_min_interval</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>combat</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>顿帧全局最小触发间隔（s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>var_knockback_per_damage</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>combat</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>16</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>100</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>受击击退力度（每点伤害）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>var_walk_speed</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>movement</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>160</v>
+      </c>
+      <c r="D28" t="n">
+        <v>40</v>
+      </c>
+      <c r="E28" t="n">
+        <v>600</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>火柴人步行速度（px/s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>var_run_speed</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>movement</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>208</v>
+      </c>
+      <c r="D29" t="n">
+        <v>40</v>
+      </c>
+      <c r="E29" t="n">
+        <v>800</v>
+      </c>
+      <c r="F29" t="n">
+        <v>5</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>火柴人跑步速度（px/s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>var_base_scale</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>movement</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>火柴人基础视觉缩放</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>var_spread_spacing</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>formation</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>32</v>
+      </c>
+      <c r="D31" t="n">
+        <v>8</v>
+      </c>
+      <c r="E31" t="n">
+        <v>128</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>散开编队间距（px）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>var_follow_default_gap</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>formation</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>150</v>
+      </c>
+      <c r="D32" t="n">
+        <v>40</v>
+      </c>
+      <c r="E32" t="n">
+        <v>400</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>跟随默认间距（px）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>var_row_gap</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>formation</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>56</v>
+      </c>
+      <c r="D33" t="n">
+        <v>16</v>
+      </c>
+      <c r="E33" t="n">
+        <v>160</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>编队列间距（px）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>var_catchup_run_dist</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>formation</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>140</v>
+      </c>
+      <c r="D34" t="n">
+        <v>40</v>
+      </c>
+      <c r="E34" t="n">
+        <v>400</v>
+      </c>
+      <c r="F34" t="n">
+        <v>5</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>跟随切跑距离（px）</t>
         </is>
       </c>
     </row>
